--- a/tasks/finalpool/fetch-howtocook-catering-budget-excel-gcal-word/groundtruth_workspace/Catering_Budget.xlsx
+++ b/tasks/finalpool/fetch-howtocook-catering-budget-excel-gcal-word/groundtruth_workspace/Catering_Budget.xlsx
@@ -708,10 +708,10 @@
         <v>6.5</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>208</v>
+        <v>187.2</v>
       </c>
     </row>
     <row r="3">
@@ -824,10 +824,10 @@
         <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>1400</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="7">
@@ -969,10 +969,10 @@
         <v>6.5</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>156</v>
+        <v>140.4</v>
       </c>
     </row>
     <row r="12">
@@ -998,10 +998,10 @@
         <v>35</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13">
@@ -1056,10 +1056,10 @@
         <v>35</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15">
@@ -1259,10 +1259,10 @@
         <v>35</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>1050</v>
+        <v>945</v>
       </c>
     </row>
     <row r="22">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>470</v>
+        <v>449.2</v>
       </c>
     </row>
     <row r="3">
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1454</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="4">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>436</v>
+        <v>392.4</v>
       </c>
     </row>
     <row r="6">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>600</v>
+        <v>572</v>
       </c>
     </row>
     <row r="7">
@@ -1518,19 +1518,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1095</v>
-      </c>
-    </row>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7827</v>
+        <v>7489.6</v>
       </c>
     </row>
   </sheetData>
